--- a/Task_3_Resources(Edge_AI).xlsx
+++ b/Task_3_Resources(Edge_AI).xlsx
@@ -601,7 +601,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="6" t="str">
-        <f>HYPERLINK("https://www.qualcomm.com/news/onq/2021/02/how-does-ai-work-edge", "Qualcomm - AI on the Edge")</f>
+        <f>HYPERLINK("https://www.qualcomm.com/news/onq/2023/09/ai-on-the-edge-the-latest-on-device-ai-insights-and-trends", "Qualcomm - AI on the Edge")</f>
         <v>Qualcomm - AI on the Edge</v>
       </c>
       <c r="F8" s="1"/>
@@ -631,7 +631,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="6" t="str">
-        <f>HYPERLINK("https://www.tensorflow.org/lite/models", "TensorFlow Lite Models")</f>
+        <f>HYPERLINK("https://developers.google.com/edge/litert/conversion/tensorflow/pretrained_models", "TensorFlow Lite Models")</f>
         <v>TensorFlow Lite Models</v>
       </c>
       <c r="F9" s="1"/>
@@ -661,8 +661,8 @@
         <v>14</v>
       </c>
       <c r="E10" s="6" t="str">
-        <f>HYPERLINK("https://mlcommons.org/en/inference-edge-30/", "MLPerf Inference Edge")</f>
-        <v>MLPerf Inference Edge</v>
+        <f>HYPERLINK("https://troylendman.com/edge-ai-chip-benchmark-metrics-that-matter/", "Troy Lendman - Edge AI Benchmarks")</f>
+        <v>Troy Lendman - Edge AI Benchmarks</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>

--- a/Task_3_Resources(Edge_AI).xlsx
+++ b/Task_3_Resources(Edge_AI).xlsx
@@ -601,8 +601,8 @@
         <v>10</v>
       </c>
       <c r="E8" s="6" t="str">
-        <f>HYPERLINK("https://www.qualcomm.com/news/onq/2023/09/ai-on-the-edge-the-latest-on-device-ai-insights-and-trends", "Qualcomm - AI on the Edge")</f>
-        <v>Qualcomm - AI on the Edge</v>
+        <f>HYPERLINK("https://milvus.io/ai-quick-reference/what-are-the-challenges-of-model-training-in-edge-ai", "Challenges of large models on the edge")</f>
+        <v>Challenges of large models on the edge</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
